--- a/public/templates/홍보신청_일괄등록_양식.xlsx
+++ b/public/templates/홍보신청_일괄등록_양식.xlsx
@@ -1,56 +1,164 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="신청내역" sheetId="1" r:id="rId1"/>
-    <sheet name="작성안내" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="신청내역" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="작성안내" state="visible" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+  <si>
+    <t>유형</t>
+  </si>
+  <si>
+    <t>제목</t>
+  </si>
+  <si>
+    <t>학과</t>
+  </si>
+  <si>
+    <t>신청자이름</t>
+  </si>
+  <si>
+    <t>신청자이메일</t>
+  </si>
+  <si>
+    <t>신청일</t>
+  </si>
+  <si>
+    <t>상태</t>
+  </si>
+  <si>
+    <t>예상배포일</t>
+  </si>
+  <si>
+    <t>게재저널</t>
+  </si>
+  <si>
+    <t>연구성과</t>
+  </si>
+  <si>
+    <t>OO 연구팀, OO 원리 규명</t>
+  </si>
+  <si>
+    <t>화학공학과</t>
+  </si>
+  <si>
+    <t>김연구</t>
+  </si>
+  <si>
+    <t>prof.kim@postech.ac.kr</t>
+  </si>
+  <si>
+    <t>2025-03-14</t>
+  </si>
+  <si>
+    <t>배포 완료</t>
+  </si>
+  <si>
+    <t>2025-03-20</t>
+  </si>
+  <si>
+    <t>Nature</t>
+  </si>
+  <si>
+    <t>수상성과</t>
+  </si>
+  <si>
+    <t>OOO 교수, OO상 수상</t>
+  </si>
+  <si>
+    <t>물리학과</t>
+  </si>
+  <si>
+    <t>이수상</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2025-09-02</t>
+  </si>
+  <si>
+    <t>신청 완료</t>
+  </si>
+  <si>
+    <t>행사 및 이벤트</t>
+  </si>
+  <si>
+    <t>OO 심포지엄 개최</t>
+  </si>
+  <si>
+    <t>컴퓨터공학과</t>
+  </si>
+  <si>
+    <t>박행사</t>
+  </si>
+  <si>
+    <t>2026-05-10</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>■ 홍보 신청 일괄 등록 양식 — 작성 안내</t>
+  </si>
+  <si>
+    <t>1) 예시 3줄을 지우고, 과거 접수 내역을 한 줄에 하나씩 입력하세요.</t>
+  </si>
+  <si>
+    <t>2) '유형' 칸을 클릭하면 드롭다운(단추)에서 선택할 수 있어요: 연구성과 / 수상성과 / 행사 및 이벤트 / 위원 선임 / 기타</t>
+  </si>
+  <si>
+    <t>3) '상태' 칸도 드롭다운: 신청 완료 / 배포 완료</t>
+  </si>
+  <si>
+    <t>4) 날짜(신청일/예상배포일)는 YYYY-MM-DD 형식 (예: 2025-03-14). 예상배포일은 비워도 됩니다.</t>
+  </si>
+  <si>
+    <t>5) '게재저널'은 연구성과일 때만 입력(선택).</t>
+  </si>
+  <si>
+    <t>6) 필수: 유형, 제목, 학과, 신청일, 상태.  (신청자이메일이 없으면 이름 기준으로 자동 생성)</t>
+  </si>
+  <si>
+    <t>7) 작성 후 '데이터 가져오기' 화면에서 업로드하면 자동 등록됩니다.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA61955"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -65,14 +173,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,216 +516,1203 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I1000"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="34.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="6.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>유형</v>
-      </c>
-      <c r="B1" t="str">
-        <v>제목</v>
-      </c>
-      <c r="C1" t="str">
-        <v>학과</v>
-      </c>
-      <c r="D1" t="str">
-        <v>신청자이름</v>
-      </c>
-      <c r="E1" t="str">
-        <v>신청자이메일</v>
-      </c>
-      <c r="F1" t="str">
-        <v>신청일</v>
-      </c>
-      <c r="G1" t="str">
-        <v>상태</v>
-      </c>
-      <c r="H1" t="str">
-        <v>예상배포일</v>
-      </c>
-      <c r="I1" t="str">
-        <v>게재저널</v>
-      </c>
-      <c r="J1" t="str">
-        <v>긴급</v>
+    <row r="1" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>연구성과</v>
-      </c>
-      <c r="B2" t="str">
-        <v>OO 연구팀, OO 원리 규명</v>
-      </c>
-      <c r="C2" t="str">
-        <v>화학공학과</v>
-      </c>
-      <c r="D2" t="str">
-        <v>김연구</v>
-      </c>
-      <c r="E2" t="str">
-        <v>prof.kim@postech.ac.kr</v>
-      </c>
-      <c r="F2" t="str">
-        <v>2025-03-14</v>
-      </c>
-      <c r="G2" t="str">
-        <v>배포 완료</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2025-03-20</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Nature</v>
-      </c>
-      <c r="J2" t="str">
-        <v>N</v>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>수상성과</v>
-      </c>
-      <c r="B3" t="str">
-        <v>OOO 교수, OO상 수상</v>
-      </c>
-      <c r="C3" t="str">
-        <v>물리학과</v>
-      </c>
-      <c r="D3" t="str">
-        <v>이수상</v>
-      </c>
-      <c r="E3" t="str">
-        <v>lee@postech.ac.kr</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="G3" t="str">
-        <v>홍보팀 검토 중</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v>N</v>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>행사 및 이벤트</v>
-      </c>
-      <c r="B4" t="str">
-        <v>OO 심포지엄 개최</v>
-      </c>
-      <c r="C4" t="str">
-        <v>컴퓨터공학과</v>
-      </c>
-      <c r="D4" t="str">
-        <v>박행사</v>
-      </c>
-      <c r="E4" t="str">
-        <v>park@postech.ac.kr</v>
-      </c>
-      <c r="F4" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="G4" t="str">
-        <v>신청 완료</v>
-      </c>
-      <c r="H4" t="str">
-        <v>2026-05-20</v>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v>Y</v>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
       </c>
     </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="500" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="505" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="509" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="512" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="513" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="514" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="515" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="516" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="517" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="518" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="519" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="520" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="521" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="522" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="523" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="524" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="525" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="526" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="527" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="528" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="529" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="530" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="531" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="532" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="533" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="534" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="535" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="536" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="537" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="538" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="539" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="540" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="541" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="542" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="543" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="544" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="545" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="546" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="547" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="548" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="549" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="550" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="551" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="552" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="553" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="554" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="555" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="556" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="557" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="558" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="559" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="560" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="561" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="562" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="563" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="564" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="565" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="566" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="567" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="568" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="569" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="570" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="571" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="572" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="573" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="574" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="575" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="576" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="577" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="578" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="579" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="580" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="581" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="582" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="583" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="584" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="585" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="586" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="587" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="588" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="589" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="590" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="591" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="595" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="596" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="601" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="605" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="606" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="607" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="609" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="610" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="611" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="612" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="613" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="614" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="615" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="616" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="617" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="618" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="619" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="620" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="621" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="622" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="623" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="624" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="625" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="626" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="627" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="628" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="629" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="630" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="631" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="632" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="633" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="634" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="635" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="636" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="637" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="638" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="639" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="640" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="641" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="642" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="643" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="644" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="645" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="646" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="647" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="648" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="649" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="650" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="651" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="652" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="653" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="654" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="655" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="656" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="657" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="658" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="659" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="660" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="661" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="662" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="663" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="664" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="665" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="666" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="667" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="668" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="669" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="670" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="671" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="672" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="673" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="674" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="675" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="676" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="677" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="678" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="679" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="680" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="681" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="682" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="683" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="684" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="685" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="686" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="687" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="688" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="689" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="690" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="691" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="692" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="693" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="694" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="695" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="696" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="697" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="698" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="699" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="700" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="701" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="702" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="703" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="704" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="705" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="706" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="707" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="708" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="709" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="710" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="711" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="712" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="713" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="714" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="715" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="716" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="717" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="718" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="719" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="720" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="721" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="722" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="723" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="724" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="725" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="726" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="727" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="728" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="729" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="730" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="731" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="732" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="733" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="734" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="735" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="736" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="737" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="738" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="739" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="740" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="741" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="742" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="743" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="744" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="745" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="746" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="747" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="748" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="749" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="750" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="751" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="752" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="753" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="754" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="755" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="756" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="757" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="758" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="759" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="760" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="761" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="762" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="763" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="764" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="765" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="766" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="767" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="768" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="769" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="770" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="771" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="772" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="773" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="774" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="775" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="776" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="777" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="778" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="779" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="780" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="781" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="782" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="783" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="784" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="785" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="786" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="787" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="788" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="789" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="790" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="791" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="792" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="793" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="794" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="795" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="796" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="797" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="798" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="799" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="800" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="801" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="802" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="803" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="804" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="805" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="806" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="807" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="808" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="809" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="810" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="811" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="812" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="813" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="814" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="815" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="816" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="817" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="818" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="819" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="820" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="821" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="822" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="823" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="824" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="825" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="826" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="827" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="828" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="829" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="830" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="831" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="832" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="833" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="834" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="835" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="836" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="837" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="838" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="839" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="840" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="841" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="842" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="843" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="844" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="845" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="846" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="847" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="848" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="849" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="850" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="851" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="852" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="853" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="854" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="855" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="856" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="857" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="858" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="859" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="860" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="861" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="862" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="863" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="864" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="865" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="866" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="867" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="868" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="869" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="870" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="871" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="872" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="873" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="874" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="875" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="876" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="877" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="878" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="879" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="880" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="881" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="882" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="883" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="884" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="885" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="886" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="887" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="888" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="889" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="890" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="891" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="892" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="893" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="894" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="895" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="896" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="897" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="898" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="899" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="900" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="901" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="902" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="903" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="904" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="905" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="906" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="907" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="908" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="909" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="910" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="911" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="912" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="913" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="914" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="915" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="916" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="917" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="918" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="919" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="920" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="921" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="922" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="923" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="924" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="925" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="926" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="927" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="928" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="929" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="930" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="931" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="932" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="933" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="934" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="935" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="936" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="937" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="938" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="939" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="940" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="941" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="942" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="943" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="944" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="945" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="946" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="947" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="948" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="949" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="950" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="951" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="952" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="953" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="954" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="955" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="956" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="957" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="958" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="959" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="960" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="961" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="962" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="963" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="964" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="965" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="966" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="967" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="968" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="969" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="970" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="971" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="972" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="973" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="974" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="975" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="976" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="977" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="978" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="979" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="980" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="981" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="982" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="983" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="984" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="985" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="986" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="987" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="988" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="989" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="990" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="991" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="992" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="993" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="994" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="995" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="996" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="997" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="998" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="999" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="1000" spans="1:7" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
-  </ignoredErrors>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" sqref="A10:A1000">
+      <formula1>"연구성과,수상성과,행사 및 이벤트,위원 선임,기타"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="A2:A1000">
+      <formula1>"연구성과,수상성과,행사 및 이벤트,위원 선임,기타"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G1000">
+      <formula1>"신청 완료,배포 완료"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G2:G1000">
+      <formula1>"신청 완료,배포 완료"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="100.83203125" customWidth="1"/>
+    <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>■ 홍보 신청 일괄 등록 양식 — 작성 안내</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1) 아래 예시 3줄을 지우고, 과거 접수 내역을 한 줄에 하나씩 입력하세요.</v>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2) '유형'은 다음 중 하나: 연구성과 / 수상성과 / 위원 선임 / 동정 / 행사 및 이벤트 / 기타</v>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3) '상태'는 다음 중 하나: 초안 작성 중 / 신청 완료 / 홍보팀 검토 중 / 자료 보완 요청 / 연구진 검토 요청 /</v>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v xml:space="preserve">    국문 최종본 확정 / 영문본 작성 중 / 영문본 검토 요청 / 연구진 수정 요청 / 최종 완료 / 배포 예정 /</v>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v xml:space="preserve">    배포 완료 / 보류 / 반려</v>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>4) 날짜(신청일/예상배포일)는 YYYY-MM-DD 형식 (예: 2025-03-14). 예상배포일은 비워도 됩니다.</v>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>5) '게재저널'은 연구성과일 때만 입력(선택). '긴급'은 Y 또는 N.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>6) 필수: 유형, 제목, 학과, 신청일, 상태.  (신청자이메일이 없으면 이름 기준으로 자동 생성)</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>7) 작성 후 이 파일을 '데이터 가져오기' 화면에서 업로드하면 자동 등록됩니다.</v>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A10"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>